--- a/APS-Modules/aps-xwyy/src/main/resources/excelModel/xwyyScheduleResult.xlsx
+++ b/APS-Modules/aps-xwyy/src/main/resources/excelModel/xwyyScheduleResult.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-xwyy\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34A261A-73C9-464B-832F-956E7300D729}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA390ED8-687A-4288-B1B6-6ECB1E079F35}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -403,43 +403,43 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -666,7 +666,7 @@
     <col min="35" max="16384" width="8.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="9.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -720,116 +720,116 @@
       </c>
     </row>
     <row r="2" spans="1:35" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="42"/>
-      <c r="W2" s="42"/>
-      <c r="X2" s="42"/>
-      <c r="Y2" s="42"/>
-      <c r="Z2" s="42"/>
-      <c r="AA2" s="42"/>
-      <c r="AB2" s="42"/>
-      <c r="AC2" s="42"/>
-      <c r="AD2" s="42"/>
-      <c r="AE2" s="42"/>
-      <c r="AF2" s="42"/>
-      <c r="AG2" s="42"/>
-      <c r="AH2" s="42"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
+      <c r="AG2" s="31"/>
+      <c r="AH2" s="31"/>
       <c r="AI2" s="26"/>
     </row>
     <row r="3" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="H3" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="43" t="s">
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="43" t="s">
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="33"/>
+      <c r="S3" s="33"/>
+      <c r="T3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="U3" s="40"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="40"/>
-      <c r="Y3" s="40"/>
-      <c r="Z3" s="43" t="s">
+      <c r="U3" s="33"/>
+      <c r="V3" s="33"/>
+      <c r="W3" s="33"/>
+      <c r="X3" s="33"/>
+      <c r="Y3" s="33"/>
+      <c r="Z3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="AA3" s="40"/>
-      <c r="AB3" s="40"/>
-      <c r="AC3" s="40"/>
-      <c r="AD3" s="40"/>
-      <c r="AE3" s="40"/>
-      <c r="AF3" s="40" t="s">
+      <c r="AA3" s="33"/>
+      <c r="AB3" s="33"/>
+      <c r="AC3" s="33"/>
+      <c r="AD3" s="33"/>
+      <c r="AE3" s="33"/>
+      <c r="AF3" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="AG3" s="33" t="s">
+      <c r="AG3" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="AH3" s="40" t="s">
+      <c r="AH3" s="33" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="40"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="33"/>
       <c r="H4" s="3" t="s">
         <v>15</v>
       </c>
@@ -902,9 +902,9 @@
       <c r="AE4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AF4" s="40"/>
-      <c r="AG4" s="33"/>
-      <c r="AH4" s="40"/>
+      <c r="AF4" s="33"/>
+      <c r="AG4" s="34"/>
+      <c r="AH4" s="33"/>
     </row>
     <row r="5" spans="1:35" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
@@ -1051,439 +1051,439 @@
       <c r="AH6" s="23"/>
     </row>
     <row r="8" spans="1:35" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
+      <c r="A8" s="41"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="39"/>
-      <c r="P8" s="39"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="37"/>
+      <c r="P8" s="37"/>
       <c r="Q8" s="13"/>
-      <c r="R8" s="39"/>
-      <c r="S8" s="39"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="39"/>
-      <c r="V8" s="39"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="37"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="37"/>
       <c r="W8" s="13"/>
-      <c r="X8" s="39"/>
-      <c r="Y8" s="39"/>
-      <c r="Z8" s="38"/>
-      <c r="AA8" s="39"/>
-      <c r="AB8" s="39"/>
+      <c r="X8" s="37"/>
+      <c r="Y8" s="37"/>
+      <c r="Z8" s="36"/>
+      <c r="AA8" s="37"/>
+      <c r="AB8" s="37"/>
       <c r="AC8" s="13"/>
-      <c r="AD8" s="39"/>
-      <c r="AE8" s="39"/>
+      <c r="AD8" s="37"/>
+      <c r="AE8" s="37"/>
       <c r="AF8" s="13"/>
       <c r="AG8" s="13"/>
       <c r="AH8" s="12"/>
     </row>
     <row r="9" spans="1:35" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="33"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
       <c r="K9" s="19"/>
       <c r="L9" s="19">
         <f>IFERROR(SUM(I5:I11)*2,"")</f>
         <v>0</v>
       </c>
-      <c r="M9" s="36"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="39"/>
-      <c r="P9" s="39"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
       <c r="Q9" s="13"/>
-      <c r="R9" s="39"/>
-      <c r="S9" s="39"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="39"/>
-      <c r="V9" s="39"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="37"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="37"/>
       <c r="W9" s="13"/>
-      <c r="X9" s="39"/>
-      <c r="Y9" s="39"/>
-      <c r="Z9" s="38"/>
-      <c r="AA9" s="39"/>
-      <c r="AB9" s="39"/>
+      <c r="X9" s="37"/>
+      <c r="Y9" s="37"/>
+      <c r="Z9" s="36"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="37"/>
       <c r="AC9" s="13"/>
-      <c r="AD9" s="39"/>
-      <c r="AE9" s="39"/>
+      <c r="AD9" s="37"/>
+      <c r="AE9" s="37"/>
       <c r="AF9" s="13"/>
       <c r="AG9" s="13"/>
       <c r="AH9" s="12"/>
     </row>
     <row r="10" spans="1:35" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="33"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
       <c r="K10" s="19"/>
       <c r="L10" s="19">
         <f>IFERROR(SUM(I6:I12)*2,"")</f>
         <v>0</v>
       </c>
-      <c r="M10" s="36"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="39"/>
-      <c r="P10" s="39"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="37"/>
+      <c r="P10" s="37"/>
       <c r="Q10" s="13"/>
-      <c r="R10" s="39"/>
-      <c r="S10" s="39"/>
-      <c r="T10" s="38"/>
-      <c r="U10" s="39"/>
-      <c r="V10" s="39"/>
+      <c r="R10" s="37"/>
+      <c r="S10" s="37"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="37"/>
+      <c r="V10" s="37"/>
       <c r="W10" s="13"/>
-      <c r="X10" s="39"/>
-      <c r="Y10" s="39"/>
-      <c r="Z10" s="38"/>
-      <c r="AA10" s="39"/>
-      <c r="AB10" s="39"/>
+      <c r="X10" s="37"/>
+      <c r="Y10" s="37"/>
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="37"/>
+      <c r="AB10" s="37"/>
       <c r="AC10" s="13"/>
-      <c r="AD10" s="39"/>
-      <c r="AE10" s="39"/>
+      <c r="AD10" s="37"/>
+      <c r="AE10" s="37"/>
       <c r="AF10" s="13"/>
       <c r="AG10" s="13"/>
       <c r="AH10" s="12"/>
     </row>
     <row r="11" spans="1:35" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="39"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="39"/>
-      <c r="V11" s="39"/>
-      <c r="W11" s="39"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="39"/>
-      <c r="Z11" s="38"/>
-      <c r="AA11" s="39"/>
-      <c r="AB11" s="39"/>
-      <c r="AC11" s="39"/>
-      <c r="AD11" s="39"/>
-      <c r="AE11" s="39"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="37"/>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37"/>
+      <c r="R11" s="37"/>
+      <c r="S11" s="37"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="37"/>
+      <c r="V11" s="37"/>
+      <c r="W11" s="37"/>
+      <c r="X11" s="37"/>
+      <c r="Y11" s="37"/>
+      <c r="Z11" s="36"/>
+      <c r="AA11" s="37"/>
+      <c r="AB11" s="37"/>
+      <c r="AC11" s="37"/>
+      <c r="AD11" s="37"/>
+      <c r="AE11" s="37"/>
       <c r="AF11" s="13"/>
       <c r="AG11" s="13"/>
       <c r="AH11" s="13"/>
     </row>
     <row r="12" spans="1:35" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="33"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="35"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="39"/>
+      <c r="P12" s="39"/>
       <c r="Q12" s="14"/>
-      <c r="R12" s="35"/>
-      <c r="S12" s="35"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="35"/>
-      <c r="V12" s="35"/>
+      <c r="R12" s="39"/>
+      <c r="S12" s="39"/>
+      <c r="T12" s="39"/>
+      <c r="U12" s="39"/>
+      <c r="V12" s="39"/>
       <c r="W12" s="14"/>
-      <c r="X12" s="35"/>
-      <c r="Y12" s="35"/>
-      <c r="Z12" s="35"/>
-      <c r="AA12" s="35"/>
-      <c r="AB12" s="35"/>
+      <c r="X12" s="39"/>
+      <c r="Y12" s="39"/>
+      <c r="Z12" s="39"/>
+      <c r="AA12" s="39"/>
+      <c r="AB12" s="39"/>
       <c r="AC12" s="14"/>
-      <c r="AD12" s="35"/>
-      <c r="AE12" s="35"/>
+      <c r="AD12" s="39"/>
+      <c r="AE12" s="39"/>
       <c r="AF12" s="14"/>
       <c r="AG12" s="14"/>
       <c r="AH12" s="14"/>
     </row>
     <row r="13" spans="1:35" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="33"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
       <c r="Q13" s="14"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="35"/>
-      <c r="V13" s="35"/>
+      <c r="R13" s="39"/>
+      <c r="S13" s="39"/>
+      <c r="T13" s="39"/>
+      <c r="U13" s="39"/>
+      <c r="V13" s="39"/>
       <c r="W13" s="14"/>
-      <c r="X13" s="35"/>
-      <c r="Y13" s="35"/>
-      <c r="Z13" s="35"/>
-      <c r="AA13" s="35"/>
-      <c r="AB13" s="35"/>
+      <c r="X13" s="39"/>
+      <c r="Y13" s="39"/>
+      <c r="Z13" s="39"/>
+      <c r="AA13" s="39"/>
+      <c r="AB13" s="39"/>
       <c r="AC13" s="14"/>
-      <c r="AD13" s="35"/>
-      <c r="AE13" s="35"/>
+      <c r="AD13" s="39"/>
+      <c r="AE13" s="39"/>
       <c r="AF13" s="14"/>
       <c r="AG13" s="14"/>
       <c r="AH13" s="14"/>
     </row>
     <row r="14" spans="1:35" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="39"/>
       <c r="Q14" s="14"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="35"/>
-      <c r="V14" s="35"/>
+      <c r="R14" s="39"/>
+      <c r="S14" s="39"/>
+      <c r="T14" s="39"/>
+      <c r="U14" s="39"/>
+      <c r="V14" s="39"/>
       <c r="W14" s="14"/>
-      <c r="X14" s="35"/>
-      <c r="Y14" s="35"/>
-      <c r="Z14" s="35"/>
-      <c r="AA14" s="35"/>
-      <c r="AB14" s="35"/>
+      <c r="X14" s="39"/>
+      <c r="Y14" s="39"/>
+      <c r="Z14" s="39"/>
+      <c r="AA14" s="39"/>
+      <c r="AB14" s="39"/>
       <c r="AC14" s="14"/>
-      <c r="AD14" s="35"/>
-      <c r="AE14" s="35"/>
+      <c r="AD14" s="39"/>
+      <c r="AE14" s="39"/>
       <c r="AF14" s="14"/>
       <c r="AG14" s="14"/>
       <c r="AH14" s="14"/>
     </row>
     <row r="15" spans="1:35" s="1" customFormat="1" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="33"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="35"/>
-      <c r="V15" s="35"/>
-      <c r="W15" s="35"/>
-      <c r="X15" s="35"/>
-      <c r="Y15" s="35"/>
-      <c r="Z15" s="35"/>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="35"/>
-      <c r="AC15" s="35"/>
-      <c r="AD15" s="35"/>
-      <c r="AE15" s="35"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="39"/>
+      <c r="T15" s="39"/>
+      <c r="U15" s="39"/>
+      <c r="V15" s="39"/>
+      <c r="W15" s="39"/>
+      <c r="X15" s="39"/>
+      <c r="Y15" s="39"/>
+      <c r="Z15" s="39"/>
+      <c r="AA15" s="39"/>
+      <c r="AB15" s="39"/>
+      <c r="AC15" s="39"/>
+      <c r="AD15" s="39"/>
+      <c r="AE15" s="39"/>
       <c r="AF15" s="14"/>
       <c r="AG15" s="14"/>
       <c r="AH15" s="15"/>
     </row>
     <row r="16" spans="1:35" s="1" customFormat="1" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="33"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="40"/>
       <c r="Q16" s="11"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="31"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="31"/>
-      <c r="V16" s="31"/>
+      <c r="R16" s="40"/>
+      <c r="S16" s="40"/>
+      <c r="T16" s="34"/>
+      <c r="U16" s="40"/>
+      <c r="V16" s="40"/>
       <c r="W16" s="11"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="31"/>
-      <c r="Z16" s="33"/>
-      <c r="AA16" s="31"/>
-      <c r="AB16" s="31"/>
+      <c r="X16" s="40"/>
+      <c r="Y16" s="40"/>
+      <c r="Z16" s="34"/>
+      <c r="AA16" s="40"/>
+      <c r="AB16" s="40"/>
       <c r="AC16" s="11"/>
-      <c r="AD16" s="31"/>
-      <c r="AE16" s="31"/>
+      <c r="AD16" s="40"/>
+      <c r="AE16" s="40"/>
       <c r="AF16" s="11"/>
       <c r="AG16" s="11"/>
       <c r="AH16" s="16"/>
     </row>
     <row r="17" spans="1:34" s="1" customFormat="1" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="40"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="40"/>
       <c r="Q17" s="11"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="31"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="31"/>
+      <c r="R17" s="40"/>
+      <c r="S17" s="40"/>
+      <c r="T17" s="34"/>
+      <c r="U17" s="40"/>
+      <c r="V17" s="40"/>
       <c r="W17" s="11"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="33"/>
-      <c r="AA17" s="31"/>
-      <c r="AB17" s="31"/>
+      <c r="X17" s="40"/>
+      <c r="Y17" s="40"/>
+      <c r="Z17" s="34"/>
+      <c r="AA17" s="40"/>
+      <c r="AB17" s="40"/>
       <c r="AC17" s="11"/>
-      <c r="AD17" s="31"/>
-      <c r="AE17" s="31"/>
+      <c r="AD17" s="40"/>
+      <c r="AE17" s="40"/>
       <c r="AF17" s="11"/>
       <c r="AG17" s="11"/>
       <c r="AH17" s="16"/>
     </row>
     <row r="18" spans="1:34" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="33"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="31"/>
-      <c r="P18" s="31"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="40"/>
+      <c r="P18" s="40"/>
       <c r="Q18" s="11"/>
-      <c r="R18" s="31"/>
-      <c r="S18" s="31"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="31"/>
-      <c r="V18" s="31"/>
+      <c r="R18" s="40"/>
+      <c r="S18" s="40"/>
+      <c r="T18" s="34"/>
+      <c r="U18" s="40"/>
+      <c r="V18" s="40"/>
       <c r="W18" s="11"/>
-      <c r="X18" s="31"/>
-      <c r="Y18" s="31"/>
-      <c r="Z18" s="33"/>
-      <c r="AA18" s="31"/>
-      <c r="AB18" s="31"/>
+      <c r="X18" s="40"/>
+      <c r="Y18" s="40"/>
+      <c r="Z18" s="34"/>
+      <c r="AA18" s="40"/>
+      <c r="AB18" s="40"/>
       <c r="AC18" s="11"/>
-      <c r="AD18" s="31"/>
-      <c r="AE18" s="31"/>
+      <c r="AD18" s="40"/>
+      <c r="AE18" s="40"/>
       <c r="AF18" s="11"/>
       <c r="AG18" s="11"/>
       <c r="AH18" s="11"/>
     </row>
     <row r="19" spans="1:34" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="33"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="31"/>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="31"/>
-      <c r="T19" s="33"/>
-      <c r="U19" s="31"/>
-      <c r="V19" s="31"/>
-      <c r="W19" s="31"/>
-      <c r="X19" s="31"/>
-      <c r="Y19" s="31"/>
-      <c r="Z19" s="33"/>
-      <c r="AA19" s="31"/>
-      <c r="AB19" s="31"/>
-      <c r="AC19" s="31"/>
-      <c r="AD19" s="31"/>
-      <c r="AE19" s="31"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="40"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="40"/>
+      <c r="S19" s="40"/>
+      <c r="T19" s="34"/>
+      <c r="U19" s="40"/>
+      <c r="V19" s="40"/>
+      <c r="W19" s="40"/>
+      <c r="X19" s="40"/>
+      <c r="Y19" s="40"/>
+      <c r="Z19" s="34"/>
+      <c r="AA19" s="40"/>
+      <c r="AB19" s="40"/>
+      <c r="AC19" s="40"/>
+      <c r="AD19" s="40"/>
+      <c r="AE19" s="40"/>
       <c r="AF19" s="11"/>
       <c r="AG19" s="11"/>
       <c r="AH19" s="11"/>
@@ -1498,60 +1498,46 @@
     </row>
   </sheetData>
   <mergeCells count="119">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="H2:AH2"/>
-    <mergeCell ref="H3:M3"/>
-    <mergeCell ref="N3:S3"/>
-    <mergeCell ref="T3:Y3"/>
-    <mergeCell ref="Z3:AE3"/>
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="AG3:AG4"/>
-    <mergeCell ref="AH3:AH4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="T8:T11"/>
-    <mergeCell ref="AD8:AE8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AD9:AE9"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AD10:AE10"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="AA11:AC11"/>
-    <mergeCell ref="AD11:AE11"/>
-    <mergeCell ref="Z8:Z11"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="T12:T15"/>
-    <mergeCell ref="Z12:Z15"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="A8:G19"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="H16:H19"/>
+    <mergeCell ref="M8:M10"/>
+    <mergeCell ref="M12:M14"/>
+    <mergeCell ref="M16:M18"/>
+    <mergeCell ref="N8:N11"/>
+    <mergeCell ref="N12:N15"/>
+    <mergeCell ref="N16:N19"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="U19:W19"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="AA19:AC19"/>
+    <mergeCell ref="AD19:AE19"/>
+    <mergeCell ref="T16:T19"/>
+    <mergeCell ref="Z16:Z19"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="AA14:AB14"/>
+    <mergeCell ref="AD14:AE14"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="AA15:AC15"/>
+    <mergeCell ref="AD15:AE15"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AD17:AE17"/>
+    <mergeCell ref="AD18:AE18"/>
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="O17:P17"/>
     <mergeCell ref="R17:S17"/>
@@ -1576,47 +1562,61 @@
     <mergeCell ref="L15:M15"/>
     <mergeCell ref="O15:Q15"/>
     <mergeCell ref="R15:S15"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AD10:AE10"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="AA11:AC11"/>
+    <mergeCell ref="AD11:AE11"/>
+    <mergeCell ref="Z8:Z11"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="T12:T15"/>
+    <mergeCell ref="Z12:Z15"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="X12:Y12"/>
     <mergeCell ref="U15:W15"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="AA14:AB14"/>
-    <mergeCell ref="AD14:AE14"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="AA15:AC15"/>
-    <mergeCell ref="AD15:AE15"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AD17:AE17"/>
-    <mergeCell ref="AD18:AE18"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="U19:W19"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="AA19:AC19"/>
-    <mergeCell ref="AD19:AE19"/>
-    <mergeCell ref="T16:T19"/>
-    <mergeCell ref="Z16:Z19"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="A8:G19"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="H16:H19"/>
-    <mergeCell ref="M8:M10"/>
-    <mergeCell ref="M12:M14"/>
-    <mergeCell ref="M16:M18"/>
-    <mergeCell ref="N8:N11"/>
-    <mergeCell ref="N12:N15"/>
-    <mergeCell ref="N16:N19"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="T8:T11"/>
+    <mergeCell ref="AD8:AE8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AD9:AE9"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="H2:AH2"/>
+    <mergeCell ref="H3:M3"/>
+    <mergeCell ref="N3:S3"/>
+    <mergeCell ref="T3:Y3"/>
+    <mergeCell ref="Z3:AE3"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="AG3:AG4"/>
+    <mergeCell ref="AH3:AH4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="1">
